--- a/separated_by_section/SECTION_SUMMARY.xlsx
+++ b/separated_by_section/SECTION_SUMMARY.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Primary Section</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>652</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88731</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>69164</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>85785</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="C3" t="n">
-        <v>52886</v>
+        <v>66609</v>
       </c>
       <c r="D3" t="n">
-        <v>37648</v>
+        <v>48293</v>
       </c>
       <c r="E3" t="n">
-        <v>48849</v>
+        <v>61723</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>148</v>
+        <v>250</v>
       </c>
       <c r="C4" t="n">
-        <v>48499</v>
+        <v>61082</v>
       </c>
       <c r="D4" t="n">
-        <v>35835</v>
+        <v>46518</v>
       </c>
       <c r="E4" t="n">
-        <v>47761</v>
+        <v>60014</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>363</v>
+        <v>711</v>
       </c>
       <c r="C5" t="n">
-        <v>10158</v>
+        <v>39674</v>
       </c>
       <c r="D5" t="n">
-        <v>8580</v>
+        <v>31741</v>
       </c>
       <c r="E5" t="n">
-        <v>9760</v>
+        <v>37982</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C6" t="n">
-        <v>15079</v>
+        <v>15456</v>
       </c>
       <c r="D6" t="n">
-        <v>11245</v>
+        <v>11550</v>
       </c>
       <c r="E6" t="n">
-        <v>14550</v>
+        <v>14929</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="C7" t="n">
-        <v>37773</v>
+        <v>70263</v>
       </c>
       <c r="D7" t="n">
-        <v>26855</v>
+        <v>51197</v>
       </c>
       <c r="E7" t="n">
-        <v>36412</v>
+        <v>68441</v>
       </c>
     </row>
   </sheetData>
